--- a/StatPub/AltMetric.xlsx
+++ b/StatPub/AltMetric.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10517"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10914"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jeremycarlot/Documents/Website/JayCrlt.github.io/StatPub/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8907F35B-9BEE-D84A-8C71-81E0D556D18D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1224601-223A-714A-966F-99826D4185CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="660" windowWidth="24300" windowHeight="15040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="65">
   <si>
     <t>doi</t>
   </si>
@@ -209,6 +209,12 @@
   </si>
   <si>
     <t>QIV2ME_5wuYC</t>
+  </si>
+  <si>
+    <t>10.1002/oik.11371</t>
+  </si>
+  <si>
+    <t>WF5omc3nYNoC</t>
   </si>
 </sst>
 </file>
@@ -562,7 +568,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="10.83203125" customWidth="1"/>
@@ -876,6 +882,17 @@
         <v>0</v>
       </c>
     </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>63</v>
+      </c>
+      <c r="B24" t="s">
+        <v>64</v>
+      </c>
+      <c r="D24">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/StatPub/AltMetric.xlsx
+++ b/StatPub/AltMetric.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jeremycarlot/Documents/Website/JayCrlt.github.io/StatPub/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1224601-223A-714A-966F-99826D4185CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D96A9C4-018D-1745-B2A1-2276F6929E40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="660" windowWidth="24300" windowHeight="15040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -889,8 +889,11 @@
       <c r="B24" t="s">
         <v>64</v>
       </c>
+      <c r="C24">
+        <v>204056161</v>
+      </c>
       <c r="D24">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
